--- a/backend/data/financials_by_company/0235.HK.xlsx
+++ b/backend/data/financials_by_company/0235.HK.xlsx
@@ -3872,7 +3872,7 @@
         <v>-13268000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
